--- a/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
@@ -134,5 +134,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C5"/>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="C2:C5">
+      <formula1>ISNUMBER(C2)</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
@@ -135,7 +135,7 @@
   </sheetData>
   <autoFilter ref="A1:C5"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" sqref="C2:C5">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="C2:C5">
       <formula1>ISNUMBER(C2)</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -140,4 +140,14 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Name"/>
+    <column index="2" property="Email"/>
+    <column index="3" property="Salary"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
+++ b/src/Excelsior.Tests/AnonymousTypeTests.Test.verified.xlsx
@@ -52,7 +52,7 @@
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
